--- a/submit/VBot_baogia.xlsx
+++ b/submit/VBot_baogia.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BaoGia" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="375">
   <si>
     <t xml:space="preserve">Component</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Sinh ảnh cấp 5: Stability Stable Image Core 1.0</t>
   </si>
   <si>
-    <t xml:space="preserve">us-west-2 (Singapore không có dịch vụ sinh ảnh; Titan Image không còn trong bảng model theo vùng, Nova Canvas đã hết hạn 2026-09-30); 55.000 request cấp 5 × 1,03 (lượt hỏi lại) × 2 ảnh = 113.300 ảnh × 0,04 USD = 4532.00. Chỉ gửi mô tả văn bản ra us-west-2</t>
+    <t xml:space="preserve">us-west-2 (Singapore không có dịch vụ sinh ảnh; Titan Image không còn trong bảng model theo vùng, Nova Canvas đã hết hạn 2026-09-30). ĐÃ CHỐT: mỗi request cấp 5 chỉ sinh 1 ảnh nháp, người dùng xin thêm khi cần, trung bình 1,1 ảnh/request. Ảnh = 55.000 request cấp 5/tháng (1,1 triệu × 5%) × 1,1 ảnh = 60.500 ảnh × 0,04 USD (Stable Image Core 1.0, 1 ảnh) = 2420.00. Chỉ gửi mô tả văn bản ra us-west-2</t>
   </si>
   <si>
     <t xml:space="preserve">E24; E26; https://aws.amazon.com/bedrock/pricing/; https://pricing.us-east-1.amazonaws.com/offers/v1.0/aws/AmazonBedrockFoundationModels/current/index.json; https://docs.aws.amazon.com/bedrock/latest/userguide/models-region-compatibility.html</t>
@@ -140,18 +140,21 @@
     <t xml:space="preserve">Lưu trữ gp3 Multi-AZ cho RDS prod</t>
   </si>
   <si>
-    <t xml:space="preserve">RDS gp3 Multi-AZ PostgreSQL, ap-southeast-1: 300 GB x 0,276 USD/GB-tháng = 82,80. Gồm vector+index ~30 GB, chat history ~132 GB/năm, metadata; IOPS/throughput nền gp3 của dung lượng này, không mua thêm. Ngày tra 2026-10-16.</t>
+    <t xml:space="preserve">RDS gp3 Multi-AZ PostgreSQL, ap-southeast-1: 300 GB x 0,276 USD/GB-tháng = 82,80. Gồm vector+index ~30 GB, lịch sử chat và bộ nhớ dài hạn ~132 GB ổn định (ĐÃ CHỐT giữ 12 tháng rồi xóa nên không tăng tiếp), metadata; IOPS/throughput nền gp3 của dung lượng này, không mua thêm. Ngày tra 2026-10-16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E40; E67; https://aws.amazon.com/rds/postgresql/pricing/; https://docs.aws.amazon.com/AmazonRDS/latest/UserGuide/PostgreSQL_pg_cron.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDS PostgreSQL staging (1 môi trường staging)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDS PostgreSQL ap-southeast-1, db.t4g.medium Single-AZ staging: 0,102 USD/giờ x 730 = 74,46 cộng gp3 50 GB x 0,138 = 6,90. Staging không cần HA. Ngày tra 2026-10-16.</t>
   </si>
   <si>
     <t xml:space="preserve">E40; https://aws.amazon.com/rds/postgresql/pricing/</t>
   </si>
   <si>
-    <t xml:space="preserve">RDS PostgreSQL staging (1 môi trường staging)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDS PostgreSQL ap-southeast-1, db.t4g.medium Single-AZ staging: 0,102 USD/giờ x 730 = 74,46 cộng gp3 50 GB x 0,138 = 6,90. Staging không cần HA. Ngày tra 2026-10-16.</t>
-  </si>
-  <si>
     <t xml:space="preserve">vector_db</t>
   </si>
   <si>
@@ -167,19 +170,31 @@
     <t xml:space="preserve">object_storage</t>
   </si>
   <si>
-    <t xml:space="preserve">S3 Standard workspace riêng từng user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S3 Standard ap-southeast-1: 2.000 user x 2 GB trung bình = 4.000 GB x 0,025 USD/GB-tháng = 100,00. Một bucket, prefix users/{user_id}/, quota 10 GB/user áp ở tầng ứng dụng. Chưa tính SSE-KMS (xem secrets_kms). Ngày tra 2026-10-16.</t>
+    <t xml:space="preserve">S3 Standard workspace riêng từng user (gồm phiên bản cũ 7 ngày)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 Standard ap-southeast-1: 2.000 user x 2 GB trung bình = 4.000 GB, cộng phiên bản cũ giữ 7 ngày do bật versioning (cần cho CRR và xóa theo chính sách ĐÃ CHỐT): 200 GB/tháng bị ghi đè hoặc xóa x 7/30 = 46,7 GB; tổng 4.046,7 GB x 0,025 USD/GB-tháng = 101,17. Một bucket, prefix users/{user_id}/; quota 10 GB/user ở tầng ứng dụng. Lifecycle NoncurrentVersionExpiration 7 ngày ở cả bucket Singapore và Sydney. Chưa tính SSE-KMS (xem secrets_kms). Ngày tra 2026-10-16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E43; E65; E66; https://aws.amazon.com/s3/pricing/; https://docs.aws.amazon.com/AmazonS3/latest/userguide/object-lifecycle-mgmt.html; https://docs.aws.amazon.com/AmazonS3/latest/userguide/replication-what-is-isnot-replicated.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 request PUT/GET và staging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 ap-southeast-1: 4 triệu PUT/LIST x 0,005 USD/1000 = 20,00 cộng 20 triệu GET x 0,0004 USD/1000 = 8,00; bucket staging ~50 GB x 0,025 = 1,25 (đã gồm trong 29,25 làm tròn). Ngày tra 2026-10-16.</t>
   </si>
   <si>
     <t xml:space="preserve">E43; https://aws.amazon.com/s3/pricing/</t>
   </si>
   <si>
-    <t xml:space="preserve">S3 request PUT/GET và staging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S3 ap-southeast-1: 4 triệu PUT/LIST x 0,005 USD/1000 = 20,00 cộng 20 triệu GET x 0,0004 USD/1000 = 8,00; bucket staging ~50 GB x 0,025 = 1,25 (đã gồm trong 29,25 làm tròn). Ngày tra 2026-10-16.</t>
+    <t xml:space="preserve">Nhãn phân loại dữ liệu (Công khai/Nội bộ/Mật) trên object S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3 ap-southeast-1 lưu trữ object tag: 1.000.000 object workspace (giả định) x 0,0065 USD/10.000 tag-tháng = 0,65. Nhãn gắn lúc PutObject (không thêm request) để dùng cho điều kiện IAM và lọc. Chỉ có trong Price List JSON, trang giá chưa thấy: CHƯA CÓ BẰNG CHỨNG trên trang. Tag được sao chép sang Sydney (tính ở backup_dr của phần C). Ngày tra 2026-10-16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E69; https://aws.amazon.com/s3/pricing/</t>
   </si>
   <si>
     <t xml:space="preserve">cache_queue</t>
@@ -335,7 +350,10 @@
     <t xml:space="preserve">Audit log 12 tháng trên S3 Object Lock</t>
   </si>
   <si>
-    <t xml:space="preserve">S3 Standard ap-southeast-1: 22 GB log/tháng x 12 tháng = 264 GB x 0,025 USD/GB-tháng = 6,60 (trạng thái ổn định tháng 12). Object Lock chế độ compliance, mã hóa SSE-KMS. Ngày tra 2026-10-16.</t>
+    <t xml:space="preserve">S3 Standard ap-southeast-1: 22 GB log/tháng x 12 tháng = 264 GB x 0,025 USD/GB-tháng = 6,60 (trạng thái ổn định). ĐÃ CHỐT audit 12 tháng: bucket bật versioning, Object Lock chế độ compliance, retention mặc định 365 ngày, lifecycle expiration 366 ngày; SSE-KMS; chỉ lưu nội dung đã che PII (mức Mật chỉ lưu siêu dữ liệu). Ngày tra 2026-10-16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E43; E64; E65; https://aws.amazon.com/s3/pricing/; https://docs.aws.amazon.com/AmazonS3/latest/userguide/object-lock.html; https://docs.aws.amazon.com/AmazonS3/latest/userguide/object-lifecycle-mgmt.html</t>
   </si>
   <si>
     <t xml:space="preserve">compute</t>
@@ -404,7 +422,7 @@
     <t xml:space="preserve">NAT Gateway: dữ liệu xử lý</t>
   </si>
   <si>
-    <t xml:space="preserve">ap-southeast-1. 207 GB/tháng × 0.059 USD/GB: 88 GB connector (uoc-luong-tai) + ~57 GB ảnh trả về từ Stable Image Core ở us-west-2 (113,300 ảnh × 500 KB, phần A; gọi bedrock-runtime.us-west-2 qua NAT vì endpoint riêng chỉ có ở Singapore) + ~62 GB webhook, kéo image, cập nhật. Phí truyền ra từ us-west-2 (nếu AWS tính): CHƯA CÓ BẰNG CHỨNG, không cộng [CHƯA CÓ BẰNG CHỨNG trên trang: giá lấy từ Price List, trang tải tự động không hiện số Singapore; ảnh chưa chụp]</t>
+    <t xml:space="preserve">ap-southeast-1. 181 GB/tháng × 0.059 USD/GB: 88 GB connector (uoc-luong-tai) + ~31 GB ảnh trả về từ Stable Image Core ở us-west-2 (1,1 ảnh/request đã chốt: 62,315 ảnh × 500 KB, phần A; gọi bedrock-runtime.us-west-2 qua NAT vì endpoint riêng chỉ có ở Singapore) + ~62 GB webhook, kéo image, cập nhật. Phí truyền ra từ us-west-2 (nếu AWS tính): CHƯA CÓ BẰNG CHỨNG, không cộng [CHƯA CÓ BẰNG CHỨNG trên trang: giá lấy từ Price List, trang tải tự động không hiện số Singapore; ảnh chưa chụp]</t>
   </si>
   <si>
     <t xml:space="preserve">VPC interface endpoint: Bedrock Runtime, STS, KMS, Logs, SQS</t>
@@ -437,7 +455,7 @@
     <t xml:space="preserve">Truyền dữ liệu ra internet cho người dùng</t>
   </si>
   <si>
-    <t xml:space="preserve">ap-southeast-1. 200 GB/tháng (phản hồi SSE ~7 GB, file DOCX/PPTX/XLSX tải về, ~55 GB ảnh sinh ra cho cấp 5) × 0.12 USD/GB bậc đầu 10 TB. Tính đủ toàn bộ 200 GB, không trừ hạn mức nào [CHƯA CÓ BẰNG CHỨNG trên trang: giá lấy từ Price List, trang tải tự động không hiện số Singapore; ảnh chưa chụp]</t>
+    <t xml:space="preserve">ap-southeast-1. 176 GB/tháng (phản hồi SSE ~7 GB, file DOCX/PPTX/XLSX tải về, ~31 GB ảnh sinh ra cho cấp 5 ở mức 1,1 ảnh/request) × 0.12 USD/GB bậc đầu 10 TB. Tính đủ toàn bộ 176 GB, không trừ hạn mức nào [CHƯA CÓ BẰNG CHỨNG trên trang: giá lấy từ Price List, trang tải tự động không hiện số Singapore; ảnh chưa chụp]</t>
   </si>
   <si>
     <t xml:space="preserve">Route 53 (DNS)</t>
@@ -620,7 +638,7 @@
     <t xml:space="preserve">Dự phòng 5% trên chi phí hạ tầng phần C (không gồm nhân sự)</t>
   </si>
   <si>
-    <t xml:space="preserve">5% × tổng các dòng compute, load_balancer, network, backup_dr, monitoring, cicd, licenses của phần C (705.38 USD). Lý do: đơn giá AWS niêm yết cố định, rủi ro nằm ở khối lượng (log, truyền dữ liệu, task). Khi ghép bài tính lại 5% trên toàn bộ dòng không phải nhân sự của A+B+C</t>
+    <t xml:space="preserve">5% × tổng các dòng compute, load_balancer, network, backup_dr, monitoring, cicd, licenses của phần C (700.97 USD). Lý do: đơn giá AWS niêm yết cố định, rủi ro nằm ở khối lượng (log, truyền dữ liệu, task). Khi ghép bài tính lại 5% trên toàn bộ dòng không phải nhân sự của A+B+C</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1086,6 +1104,48 @@
   </si>
   <si>
     <t xml:space="preserve">https://microsoft.github.io/presidio/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon S3 Object Lock (chế độ compliance, retention mặc định)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.aws.amazon.com/AmazonS3/latest/userguide/object-lock.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon S3 Lifecycle (expiration, chuyển lớp lưu trữ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.aws.amazon.com/AmazonS3/latest/userguide/object-lifecycle-mgmt.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon S3 Replication: thứ được và không được sao chép</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.aws.amazon.com/AmazonS3/latest/userguide/replication-what-is-isnot-replicated.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon RDS for PostgreSQL: tiện ích pg_cron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.aws.amazon.com/AmazonRDS/latest/UserGuide/PostgreSQL_pg_cron.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon S3, giá object tagging, Singapore</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1570,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1616,7 +1676,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4532</v>
+        <v>2420</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>20</v>
@@ -1707,7 +1767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -1738,942 +1798,959 @@
         <v>81.36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>100</v>
+        <v>101.17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>29.25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>56.06</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>28.03</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4</v>
+        <v>28.03</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="92.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="92.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>649.79</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>19.72</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>35.98</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="B25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>5.42</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.45</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="B29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>14.4</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>15.3</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="92.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="92.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="3" t="n">
         <v>792</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="B32" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>71.96</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="3" t="n">
         <v>10.84</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>68.51</v>
+        <v>6.6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v>68.51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>111.89</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="E36" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="3" t="n">
+      <c r="B37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="3" t="n">
         <v>10.84</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" s="3" t="n">
+    </row>
+    <row r="38" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="3" t="n">
+      <c r="B40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>86.14</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>12.21</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" s="3" t="n">
+      <c r="B43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>94.9</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D47" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>38</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="3" t="n">
+    </row>
+    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="79.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D52" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="3" t="n">
+    </row>
+    <row r="54" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>1.48</v>
-      </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>0.45</v>
-      </c>
       <c r="E57" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D58" s="3" t="n">
+      <c r="B59" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D59" s="3" t="n">
+    </row>
+    <row r="60" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D63" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="66.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D64" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D64" s="3" t="n">
+      <c r="E64" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D65" s="3" t="n">
+      <c r="E65" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="3" t="n">
         <v>1750</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="E66" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" s="3" t="n">
+      <c r="B67" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>35.27</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="5" t="n">
-        <f aca="false">SUM(D2:D67)</f>
-        <v>20986.76</v>
-      </c>
-      <c r="E68" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="5" t="n">
+        <f aca="false">SUM(D2:D68)</f>
+        <v>18871.95</v>
+      </c>
+      <c r="E69" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A2:A67" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A2:A68" type="list">
       <formula1>"compute,llm,embedding,gateway,load_balancer,authn,authz,database,vector_db,object_storage,cache_queue,sandbox,connectors,secrets_kms,backup_dr,monitoring,governance,network,cicd,ops_labor,licenses,contingency,other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2693,7 +2770,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -2705,1056 +2782,1141 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="40.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
